--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127291074</v>
+        <v>127291394</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>75130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450456</v>
+        <v>450477</v>
       </c>
       <c r="R3" t="n">
-        <v>7085105</v>
+        <v>7085044</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127291394</v>
+        <v>127291074</v>
       </c>
       <c r="B4" t="n">
-        <v>75130</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450477</v>
+        <v>450456</v>
       </c>
       <c r="R4" t="n">
-        <v>7085044</v>
+        <v>7085105</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127292608</v>
+        <v>127292733</v>
       </c>
       <c r="B12" t="n">
-        <v>91343</v>
+        <v>92022</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450884</v>
+        <v>450986</v>
       </c>
       <c r="R12" t="n">
-        <v>7084536</v>
+        <v>7084498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,32 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127292733</v>
+        <v>127292608</v>
       </c>
       <c r="B13" t="n">
-        <v>92022</v>
+        <v>91343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450986</v>
+        <v>450884</v>
       </c>
       <c r="R13" t="n">
-        <v>7084498</v>
+        <v>7084536</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>127291159</v>
       </c>
       <c r="B5" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127292514</v>
       </c>
       <c r="B6" t="n">
-        <v>95880</v>
+        <v>95881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127292902</v>
       </c>
       <c r="B8" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127292299</v>
+        <v>127291243</v>
       </c>
       <c r="B10" t="n">
-        <v>91343</v>
+        <v>91340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450768</v>
+        <v>450470</v>
       </c>
       <c r="R10" t="n">
-        <v>7084662</v>
+        <v>7085056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127291243</v>
+        <v>127292299</v>
       </c>
       <c r="B11" t="n">
-        <v>91339</v>
+        <v>91344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,34 +1604,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450470</v>
+        <v>450768</v>
       </c>
       <c r="R11" t="n">
-        <v>7085056</v>
+        <v>7084662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127292733</v>
+        <v>127292608</v>
       </c>
       <c r="B12" t="n">
-        <v>92022</v>
+        <v>91344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450986</v>
+        <v>450884</v>
       </c>
       <c r="R12" t="n">
-        <v>7084498</v>
+        <v>7084536</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,32 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127292608</v>
+        <v>127292733</v>
       </c>
       <c r="B13" t="n">
-        <v>91343</v>
+        <v>92023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450884</v>
+        <v>450986</v>
       </c>
       <c r="R13" t="n">
-        <v>7084536</v>
+        <v>7084498</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
         <v>127291169</v>
       </c>
       <c r="B14" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127291178</v>
       </c>
       <c r="B15" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127291394</v>
+        <v>127291074</v>
       </c>
       <c r="B3" t="n">
-        <v>75130</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450477</v>
+        <v>450456</v>
       </c>
       <c r="R3" t="n">
-        <v>7085044</v>
+        <v>7085105</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127291074</v>
+        <v>127291394</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>75130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450456</v>
+        <v>450477</v>
       </c>
       <c r="R4" t="n">
-        <v>7085105</v>
+        <v>7085044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127291243</v>
+        <v>127292299</v>
       </c>
       <c r="B10" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450470</v>
+        <v>450768</v>
       </c>
       <c r="R10" t="n">
-        <v>7085056</v>
+        <v>7084662</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127292299</v>
+        <v>127291243</v>
       </c>
       <c r="B11" t="n">
-        <v>91344</v>
+        <v>91340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,34 +1604,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450768</v>
+        <v>450470</v>
       </c>
       <c r="R11" t="n">
-        <v>7084662</v>
+        <v>7085056</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127292299</v>
+        <v>127291243</v>
       </c>
       <c r="B10" t="n">
-        <v>91344</v>
+        <v>91340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450768</v>
+        <v>450470</v>
       </c>
       <c r="R10" t="n">
-        <v>7084662</v>
+        <v>7085056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127291243</v>
+        <v>127292299</v>
       </c>
       <c r="B11" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,34 +1604,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450470</v>
+        <v>450768</v>
       </c>
       <c r="R11" t="n">
-        <v>7085056</v>
+        <v>7084662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127291243</v>
+        <v>127292299</v>
       </c>
       <c r="B10" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450470</v>
+        <v>450768</v>
       </c>
       <c r="R10" t="n">
-        <v>7085056</v>
+        <v>7084662</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127292299</v>
+        <v>127291243</v>
       </c>
       <c r="B11" t="n">
-        <v>91344</v>
+        <v>91340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,34 +1604,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450768</v>
+        <v>450470</v>
       </c>
       <c r="R11" t="n">
-        <v>7084662</v>
+        <v>7085056</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127291063</v>
       </c>
       <c r="B2" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127291074</v>
+        <v>127291394</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>75134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450456</v>
+        <v>450477</v>
       </c>
       <c r="R3" t="n">
-        <v>7085105</v>
+        <v>7085044</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127291394</v>
+        <v>127291074</v>
       </c>
       <c r="B4" t="n">
-        <v>75130</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450477</v>
+        <v>450456</v>
       </c>
       <c r="R4" t="n">
-        <v>7085044</v>
+        <v>7085105</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>127291159</v>
       </c>
       <c r="B5" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127292514</v>
       </c>
       <c r="B6" t="n">
-        <v>95881</v>
+        <v>95885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127291530</v>
       </c>
       <c r="B7" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127292902</v>
       </c>
       <c r="B8" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127292407</v>
       </c>
       <c r="B9" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127292299</v>
       </c>
       <c r="B10" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>127291243</v>
       </c>
       <c r="B11" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127292608</v>
       </c>
       <c r="B12" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127292733</v>
       </c>
       <c r="B13" t="n">
-        <v>92023</v>
+        <v>92027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>127291169</v>
       </c>
       <c r="B14" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127291178</v>
       </c>
       <c r="B15" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -981,45 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127291159</v>
+        <v>127292514</v>
       </c>
       <c r="B5" t="n">
-        <v>91348</v>
+        <v>95885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2682</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450467</v>
+        <v>450821</v>
       </c>
       <c r="R5" t="n">
-        <v>7085051</v>
+        <v>7084573</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1083,45 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127292514</v>
+        <v>127291159</v>
       </c>
       <c r="B6" t="n">
-        <v>95885</v>
+        <v>91348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2682</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450821</v>
+        <v>450467</v>
       </c>
       <c r="R6" t="n">
-        <v>7084573</v>
+        <v>7085051</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127292299</v>
+        <v>127291243</v>
       </c>
       <c r="B10" t="n">
-        <v>91348</v>
+        <v>91344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450768</v>
+        <v>450470</v>
       </c>
       <c r="R10" t="n">
-        <v>7084662</v>
+        <v>7085056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127291243</v>
+        <v>127292299</v>
       </c>
       <c r="B11" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,34 +1604,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450470</v>
+        <v>450768</v>
       </c>
       <c r="R11" t="n">
-        <v>7085056</v>
+        <v>7084662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127292608</v>
+        <v>127292733</v>
       </c>
       <c r="B12" t="n">
-        <v>91348</v>
+        <v>92027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450884</v>
+        <v>450986</v>
       </c>
       <c r="R12" t="n">
-        <v>7084536</v>
+        <v>7084498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,32 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127292733</v>
+        <v>127292608</v>
       </c>
       <c r="B13" t="n">
-        <v>92027</v>
+        <v>91348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450986</v>
+        <v>450884</v>
       </c>
       <c r="R13" t="n">
-        <v>7084498</v>
+        <v>7084536</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127291394</v>
+        <v>127291074</v>
       </c>
       <c r="B3" t="n">
-        <v>75134</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450477</v>
+        <v>450456</v>
       </c>
       <c r="R3" t="n">
-        <v>7085044</v>
+        <v>7085105</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127291074</v>
+        <v>127291394</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>75134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450456</v>
+        <v>450477</v>
       </c>
       <c r="R4" t="n">
-        <v>7085105</v>
+        <v>7085044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,45 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127292514</v>
+        <v>127291159</v>
       </c>
       <c r="B5" t="n">
-        <v>95885</v>
+        <v>91348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2682</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450821</v>
+        <v>450467</v>
       </c>
       <c r="R5" t="n">
-        <v>7084573</v>
+        <v>7085051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1083,45 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127291159</v>
+        <v>127292514</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>95885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2682</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450467</v>
+        <v>450821</v>
       </c>
       <c r="R6" t="n">
-        <v>7085051</v>
+        <v>7084573</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
         <v>127292902</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127291243</v>
+        <v>127292299</v>
       </c>
       <c r="B10" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450470</v>
+        <v>450768</v>
       </c>
       <c r="R10" t="n">
-        <v>7085056</v>
+        <v>7084662</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127292299</v>
+        <v>127291243</v>
       </c>
       <c r="B11" t="n">
-        <v>91348</v>
+        <v>91344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,34 +1604,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450768</v>
+        <v>450470</v>
       </c>
       <c r="R11" t="n">
-        <v>7084662</v>
+        <v>7085056</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127292733</v>
+        <v>127292608</v>
       </c>
       <c r="B12" t="n">
-        <v>92027</v>
+        <v>91348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450986</v>
+        <v>450884</v>
       </c>
       <c r="R12" t="n">
-        <v>7084498</v>
+        <v>7084536</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,32 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127292608</v>
+        <v>127292733</v>
       </c>
       <c r="B13" t="n">
-        <v>91348</v>
+        <v>92027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450884</v>
+        <v>450986</v>
       </c>
       <c r="R13" t="n">
-        <v>7084536</v>
+        <v>7084498</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127291063</v>
       </c>
       <c r="B2" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127291074</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127291394</v>
       </c>
       <c r="B4" t="n">
-        <v>75134</v>
+        <v>75136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127291159</v>
       </c>
       <c r="B5" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127292514</v>
       </c>
       <c r="B6" t="n">
-        <v>95885</v>
+        <v>95887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127291530</v>
       </c>
       <c r="B7" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127292902</v>
       </c>
       <c r="B8" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127292407</v>
       </c>
       <c r="B9" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127292299</v>
+        <v>127291243</v>
       </c>
       <c r="B10" t="n">
-        <v>91348</v>
+        <v>91346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450768</v>
+        <v>450470</v>
       </c>
       <c r="R10" t="n">
-        <v>7084662</v>
+        <v>7085056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127291243</v>
+        <v>127292299</v>
       </c>
       <c r="B11" t="n">
-        <v>91344</v>
+        <v>91350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,34 +1604,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450470</v>
+        <v>450768</v>
       </c>
       <c r="R11" t="n">
-        <v>7085056</v>
+        <v>7084662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1698,7 +1698,7 @@
         <v>127292608</v>
       </c>
       <c r="B12" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127292733</v>
       </c>
       <c r="B13" t="n">
-        <v>92027</v>
+        <v>92029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>127291169</v>
       </c>
       <c r="B14" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127291178</v>
       </c>
       <c r="B15" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -981,45 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127291159</v>
+        <v>127292514</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>95887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2682</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450467</v>
+        <v>450821</v>
       </c>
       <c r="R5" t="n">
-        <v>7085051</v>
+        <v>7084573</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1083,45 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127292514</v>
+        <v>127291159</v>
       </c>
       <c r="B6" t="n">
-        <v>95887</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2682</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450821</v>
+        <v>450467</v>
       </c>
       <c r="R6" t="n">
-        <v>7084573</v>
+        <v>7085051</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127292608</v>
+        <v>127292733</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>92029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450884</v>
+        <v>450986</v>
       </c>
       <c r="R12" t="n">
-        <v>7084536</v>
+        <v>7084498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,32 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127292733</v>
+        <v>127292608</v>
       </c>
       <c r="B13" t="n">
-        <v>92029</v>
+        <v>91350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450986</v>
+        <v>450884</v>
       </c>
       <c r="R13" t="n">
-        <v>7084498</v>
+        <v>7084536</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127291074</v>
+        <v>127291394</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>75136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450456</v>
+        <v>450477</v>
       </c>
       <c r="R3" t="n">
-        <v>7085105</v>
+        <v>7085044</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127291394</v>
+        <v>127291074</v>
       </c>
       <c r="B4" t="n">
-        <v>75136</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450477</v>
+        <v>450456</v>
       </c>
       <c r="R4" t="n">
-        <v>7085044</v>
+        <v>7085105</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,45 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127292514</v>
+        <v>127291159</v>
       </c>
       <c r="B5" t="n">
-        <v>95887</v>
+        <v>91350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2682</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450821</v>
+        <v>450467</v>
       </c>
       <c r="R5" t="n">
-        <v>7084573</v>
+        <v>7085051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1083,45 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127291159</v>
+        <v>127292514</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>95887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2682</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450467</v>
+        <v>450821</v>
       </c>
       <c r="R6" t="n">
-        <v>7085051</v>
+        <v>7084573</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127292733</v>
+        <v>127292608</v>
       </c>
       <c r="B12" t="n">
-        <v>92029</v>
+        <v>91350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450986</v>
+        <v>450884</v>
       </c>
       <c r="R12" t="n">
-        <v>7084498</v>
+        <v>7084536</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,32 +1797,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127292608</v>
+        <v>127292733</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>92029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450884</v>
+        <v>450986</v>
       </c>
       <c r="R13" t="n">
-        <v>7084536</v>
+        <v>7084498</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127291243</v>
+        <v>127292299</v>
       </c>
       <c r="B10" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450470</v>
+        <v>450768</v>
       </c>
       <c r="R10" t="n">
-        <v>7085056</v>
+        <v>7084662</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127292299</v>
+        <v>127291243</v>
       </c>
       <c r="B11" t="n">
-        <v>91350</v>
+        <v>91346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,34 +1604,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450768</v>
+        <v>450470</v>
       </c>
       <c r="R11" t="n">
-        <v>7084662</v>
+        <v>7085056</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -981,45 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127291159</v>
+        <v>127292514</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>95893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2682</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450467</v>
+        <v>450821</v>
       </c>
       <c r="R5" t="n">
-        <v>7085051</v>
+        <v>7084573</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1083,45 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127292514</v>
+        <v>127291159</v>
       </c>
       <c r="B6" t="n">
-        <v>95887</v>
+        <v>91356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2682</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450821</v>
+        <v>450467</v>
       </c>
       <c r="R6" t="n">
-        <v>7084573</v>
+        <v>7085051</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
         <v>127292902</v>
       </c>
       <c r="B8" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127292299</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>127291243</v>
       </c>
       <c r="B11" t="n">
-        <v>91346</v>
+        <v>91352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127292608</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127292733</v>
       </c>
       <c r="B13" t="n">
-        <v>92029</v>
+        <v>92035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>127291169</v>
       </c>
       <c r="B14" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127291178</v>
       </c>
       <c r="B15" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127291063</v>
       </c>
       <c r="B2" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127291394</v>
+        <v>127291074</v>
       </c>
       <c r="B3" t="n">
-        <v>75136</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450477</v>
+        <v>450456</v>
       </c>
       <c r="R3" t="n">
-        <v>7085044</v>
+        <v>7085105</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127291074</v>
+        <v>127291394</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>75139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450456</v>
+        <v>450477</v>
       </c>
       <c r="R4" t="n">
-        <v>7085105</v>
+        <v>7085044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>127292514</v>
       </c>
       <c r="B5" t="n">
-        <v>95893</v>
+        <v>95896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127291159</v>
       </c>
       <c r="B6" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127291530</v>
       </c>
       <c r="B7" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127292902</v>
       </c>
       <c r="B8" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127292407</v>
       </c>
       <c r="B9" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127292299</v>
       </c>
       <c r="B10" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>127291243</v>
       </c>
       <c r="B11" t="n">
-        <v>91352</v>
+        <v>91355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127292608</v>
       </c>
       <c r="B12" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127292733</v>
       </c>
       <c r="B13" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>127291169</v>
       </c>
       <c r="B14" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127291178</v>
       </c>
       <c r="B15" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127291063</v>
       </c>
       <c r="B2" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127291074</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127291394</v>
       </c>
       <c r="B4" t="n">
-        <v>75139</v>
+        <v>75145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,45 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127292514</v>
+        <v>127291159</v>
       </c>
       <c r="B5" t="n">
-        <v>95896</v>
+        <v>91367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2682</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450821</v>
+        <v>450467</v>
       </c>
       <c r="R5" t="n">
-        <v>7084573</v>
+        <v>7085051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1083,45 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127291159</v>
+        <v>127292514</v>
       </c>
       <c r="B6" t="n">
-        <v>91359</v>
+        <v>95904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2682</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450467</v>
+        <v>450821</v>
       </c>
       <c r="R6" t="n">
-        <v>7085051</v>
+        <v>7084573</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1188,7 +1188,7 @@
         <v>127291530</v>
       </c>
       <c r="B7" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127292902</v>
       </c>
       <c r="B8" t="n">
-        <v>98482</v>
+        <v>98490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127292407</v>
       </c>
       <c r="B9" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127292299</v>
       </c>
       <c r="B10" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>127291243</v>
       </c>
       <c r="B11" t="n">
-        <v>91355</v>
+        <v>91363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127292608</v>
       </c>
       <c r="B12" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127292733</v>
       </c>
       <c r="B13" t="n">
-        <v>92038</v>
+        <v>92046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>127291169</v>
       </c>
       <c r="B14" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127291178</v>
       </c>
       <c r="B15" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>127291159</v>
       </c>
       <c r="B5" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127292514</v>
       </c>
       <c r="B6" t="n">
-        <v>95904</v>
+        <v>95905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127292902</v>
       </c>
       <c r="B8" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>127292299</v>
       </c>
       <c r="B10" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>127291243</v>
       </c>
       <c r="B11" t="n">
-        <v>91363</v>
+        <v>91364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>127292608</v>
       </c>
       <c r="B12" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127292733</v>
       </c>
       <c r="B13" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>127291169</v>
       </c>
       <c r="B14" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127291178</v>
       </c>
       <c r="B15" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127291074</v>
+        <v>127291394</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>75145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450456</v>
+        <v>450477</v>
       </c>
       <c r="R3" t="n">
-        <v>7085105</v>
+        <v>7085044</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127291394</v>
+        <v>127291074</v>
       </c>
       <c r="B4" t="n">
-        <v>75145</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450477</v>
+        <v>450456</v>
       </c>
       <c r="R4" t="n">
-        <v>7085044</v>
+        <v>7085105</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127291394</v>
+        <v>127291074</v>
       </c>
       <c r="B3" t="n">
-        <v>75145</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450477</v>
+        <v>450456</v>
       </c>
       <c r="R3" t="n">
-        <v>7085044</v>
+        <v>7085105</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127291074</v>
+        <v>127291394</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>75145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450456</v>
+        <v>450477</v>
       </c>
       <c r="R4" t="n">
-        <v>7085105</v>
+        <v>7085044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>127291159</v>
       </c>
       <c r="B5" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127292514</v>
       </c>
       <c r="B6" t="n">
-        <v>95905</v>
+        <v>95906</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>127292902</v>
       </c>
       <c r="B8" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127292299</v>
+        <v>127291243</v>
       </c>
       <c r="B10" t="n">
-        <v>91368</v>
+        <v>91365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450768</v>
+        <v>450470</v>
       </c>
       <c r="R10" t="n">
-        <v>7084662</v>
+        <v>7085056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127291243</v>
+        <v>127292299</v>
       </c>
       <c r="B11" t="n">
-        <v>91364</v>
+        <v>91369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,34 +1604,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450470</v>
+        <v>450768</v>
       </c>
       <c r="R11" t="n">
-        <v>7085056</v>
+        <v>7084662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1698,7 +1698,7 @@
         <v>127292608</v>
       </c>
       <c r="B12" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127292733</v>
       </c>
       <c r="B13" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>127291169</v>
       </c>
       <c r="B14" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>127291178</v>
       </c>
       <c r="B15" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127291063</v>
+        <v>127291394</v>
       </c>
       <c r="B2" t="n">
-        <v>75153</v>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450423</v>
+        <v>450477</v>
       </c>
       <c r="R2" t="n">
-        <v>7085103</v>
+        <v>7085044</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Luckig, lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127291074</v>
+        <v>127291178</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450456</v>
+        <v>450467</v>
       </c>
       <c r="R3" t="n">
-        <v>7085105</v>
+        <v>7085051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127291394</v>
+        <v>127291243</v>
       </c>
       <c r="B4" t="n">
-        <v>75145</v>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450477</v>
+        <v>450470</v>
       </c>
       <c r="R4" t="n">
-        <v>7085044</v>
+        <v>7085056</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127291159</v>
+        <v>127291169</v>
       </c>
       <c r="B5" t="n">
-        <v>91369</v>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,45 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127292514</v>
+        <v>127291530</v>
       </c>
       <c r="B6" t="n">
-        <v>95906</v>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2682</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450821</v>
+        <v>450477</v>
       </c>
       <c r="R6" t="n">
-        <v>7084573</v>
+        <v>7084991</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Bördig, frodig och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127291530</v>
+        <v>127292407</v>
       </c>
       <c r="B7" t="n">
-        <v>80133</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,14 +1216,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bodrun, Bodrun, Jmt</t>
+          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450477</v>
+        <v>450823</v>
       </c>
       <c r="R7" t="n">
-        <v>7084991</v>
+        <v>7084599</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
+          <t>Bördig, örtrik och lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127292902</v>
+        <v>127292514</v>
       </c>
       <c r="B8" t="n">
-        <v>98492</v>
+        <v>96543</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>2682</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451050</v>
+        <v>450821</v>
       </c>
       <c r="R8" t="n">
-        <v>7084461</v>
+        <v>7084573</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,32 +1389,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127292407</v>
+        <v>127292733</v>
       </c>
       <c r="B9" t="n">
-        <v>80133</v>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450823</v>
+        <v>450986</v>
       </c>
       <c r="R9" t="n">
-        <v>7084599</v>
+        <v>7084498</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,32 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127291243</v>
+        <v>127291074</v>
       </c>
       <c r="B10" t="n">
-        <v>91365</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450470</v>
+        <v>450456</v>
       </c>
       <c r="R10" t="n">
-        <v>7085056</v>
+        <v>7085105</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127292299</v>
+        <v>127291063</v>
       </c>
       <c r="B11" t="n">
-        <v>91369</v>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,34 +1604,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
+          <t>Bodrun, Bodrun, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450768</v>
+        <v>450423</v>
       </c>
       <c r="R11" t="n">
-        <v>7084662</v>
+        <v>7085103</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
+          <t>Luckig, lövrik grannaturskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1695,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127292608</v>
+        <v>127292902</v>
       </c>
       <c r="B12" t="n">
-        <v>91369</v>
+        <v>99142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450884</v>
+        <v>451050</v>
       </c>
       <c r="R12" t="n">
-        <v>7084536</v>
+        <v>7084461</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,312 +1794,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>127292733</v>
-      </c>
-      <c r="B13" t="n">
-        <v>92048</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Nörderst Nörderstklumpen, Nörderst Nörderstklumpen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>450986</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7084498</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Bördig, örtrik och lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>127291169</v>
-      </c>
-      <c r="B14" t="n">
-        <v>91805</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Bodrun, Bodrun, Jmt</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>450467</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7085051</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>127291178</v>
-      </c>
-      <c r="B15" t="n">
-        <v>91351</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bodrun, Bodrun, Jmt</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>450467</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7085051</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Bördig, frodig och lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61434-2024 artfynd.xlsx
+++ b/artfynd/A 61434-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127291394</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127291178</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127291243</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127291169</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127291530</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127292407</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127292514</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127292733</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127291074</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127291063</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,8 +1849,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127292902</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>